--- a/data/Escenarios_Gx/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28438,7 +28438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28471,6 +28471,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Escenarios_Gx/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,66 +453,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>id_1</t>
+          <t>id_2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Profile_Chuquicamata</t>
+          <t>Profile_fixed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>id_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Profile_fixed</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>id_3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Profile_Machali</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>id_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Profile_diesel</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>hourly</t>
         </is>
@@ -16635,7 +16584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19012,4856 +18961,6 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>C0419</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>C0305</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>C0306</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>C0307</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>C0308</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>C0309</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>C0310</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>C0311</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>C0312</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>C0313</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>C0314</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>C0315</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>C0316</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>C0268</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>C0269</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>C0270</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>C0271</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>C0272</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>C0273</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>C0274</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>C0275</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>C0276</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>C0277</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>C0278</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>C0279</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>C0280</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>C0232</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>C0233</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>C0234</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>C0235</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>C0236</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>C0237</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>C0238</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>C0239</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>C0240</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>C0241</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>C0242</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>C0243</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>C0194</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>C0195</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>C0196</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>C0197</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>C0198</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>C0199</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>C0200</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>C0201</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>C0202</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>C0203</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>C0204</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>C0205</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>C0206</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>C0157</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>C0158</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>C0159</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>C0160</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>C0161</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>C0162</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>C0163</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>C0164</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>C0165</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>C0166</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>C0167</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>C0168</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>C0119</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>C0120</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>C0121</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>C0122</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>C0123</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>C0124</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>C0125</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>C0126</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>C0127</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>C0128</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>C0129</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>C0130</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>C0131</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>C0082</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>C0083</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>C0084</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>C0085</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>C0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>C0087</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>C0088</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>C0089</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>C0090</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>C0091</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>C0092</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>C0093</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>C0044</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>C0045</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>C0046</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>C0047</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>C0048</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>C0049</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>C0050</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>C0051</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>C0052</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>C0053</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>C0054</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>C0055</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>C0056</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>N2857</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>N2858</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>N2859</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>N2860</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>N2861</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>N2862</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>N2863</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>N2864</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>N2865</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>N2866</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>N2867</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>N2868</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>N2820</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>N2821</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>N2822</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>N2823</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>N2824</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>N2825</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>N2826</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>N2827</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>N2828</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>N2829</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>217</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>N2830</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>218</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>N2831</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>219</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>N2781</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>220</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>N2782</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>221</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>N2783</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>222</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>N2784</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>223</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>N2785</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>N2786</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>N2787</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>N2788</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>227</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>N2789</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>228</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>N2790</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>229</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>N2791</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>230</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>N2792</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>231</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>N2744</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>232</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>N2745</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>233</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>N2746</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>234</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>N2747</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>235</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>N2748</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>236</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>N2749</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>237</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>N2750</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>238</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>N2751</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>N2752</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>N2753</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>N2754</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>N2755</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>N2705</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>N2706</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>N2707</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>N2708</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>N2709</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>248</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>N2710</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>249</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>N2711</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>250</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>N2712</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>251</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>N2713</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>252</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>N2714</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>253</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>N2715</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>254</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>N2716</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>255</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>N2668</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>256</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>N2669</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>N2670</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>N2671</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>N2672</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>N2673</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>261</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>N2674</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>N2675</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>N2676</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>264</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>N2677</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>265</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>N2678</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>266</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>N2679</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>267</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>N2630</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>268</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>N2631</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>269</v>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>N2632</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>270</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>N2633</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>271</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>N2634</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>272</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>N2635</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>273</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>N2636</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>274</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>N2637</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>275</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>N2638</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>276</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>N2639</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>277</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>N2640</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>278</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>N2593</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>279</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>N2594</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>N2595</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>N2596</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>282</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>N2597</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>283</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>N2598</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>284</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>N2599</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>285</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>N2600</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>286</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>N2601</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>287</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>N2602</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>288</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>shift_1_1</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>shift_365_2</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>N2603</t>
         </is>
       </c>
     </row>
@@ -23876,7 +18975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23953,126 +19052,6 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>station_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LH518B_5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>station_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LH518B_6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>station_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LH518B_7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>station_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LH518B_8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>station_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LH518B_9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>station_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LH518B_10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>station_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LH518B_11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>station_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LH518B_12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>station_3</t>
         </is>
       </c>
     </row>
@@ -24087,7 +19066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25512,2916 +20491,6 @@
         </is>
       </c>
       <c r="C95" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>C0305</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>C0306</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>C0307</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>C0308</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>C0309</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>C0310</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>C0311</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>C0312</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>C0313</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>C0314</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>C0315</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>C0316</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>C0268</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>C0269</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>C0270</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>C0271</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>C0272</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>C0273</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>C0274</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>C0275</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>C0276</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>C0277</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>C0278</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>C0279</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>C0280</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>C0232</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>C0233</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>C0234</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>C0235</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>C0236</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>C0237</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>C0238</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>C0239</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>C0240</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>C0241</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>C0242</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>C0243</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>C0194</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>C0195</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>C0196</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>C0197</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>C0198</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>C0199</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>C0200</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>C0201</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>C0202</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>C0203</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>C0204</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>C0205</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>C0206</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>C0157</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>C0158</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>C0159</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>C0160</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>C0161</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>C0162</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>C0163</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>C0164</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>C0165</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>C0166</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>C0167</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>C0168</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>C0119</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>C0120</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>C0121</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>C0122</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>C0123</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>C0124</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>C0125</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>C0126</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>C0127</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>C0128</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>C0129</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>C0130</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>C0131</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>C0082</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>C0083</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>C0084</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>C0085</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>C0086</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>C0087</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>C0088</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>C0089</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>C0090</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>C0091</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>C0092</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>C0093</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>C0044</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>C0045</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>C0046</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>C0047</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>C0048</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>C0049</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>C0050</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>C0051</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>C0052</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>C0053</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>C0054</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>C0055</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>C0056</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>N2857</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>N2858</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>N2859</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>N2860</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>N2861</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>N2862</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>N2863</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>N2864</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>N2865</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>N2866</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>N2867</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>N2868</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>N2820</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>N2821</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>N2822</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>N2823</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>N2824</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>N2825</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>N2826</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>N2827</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>N2828</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>N2829</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>217</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>N2830</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>218</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>N2831</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>219</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>N2781</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>220</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>N2782</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>221</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>N2783</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>222</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>N2784</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>223</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>N2785</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>N2786</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>N2787</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>N2788</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>227</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>N2789</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>228</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>N2790</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>229</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>N2791</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>230</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>N2792</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>231</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>N2744</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>232</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>N2745</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>233</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>N2746</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>234</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>N2747</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>235</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>N2748</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>236</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>N2749</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>237</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>N2750</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>238</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>N2751</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>N2752</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>N2753</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>N2754</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>N2755</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>N2705</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>N2706</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>N2707</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>N2708</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>N2709</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>248</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>N2710</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>249</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>N2711</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>250</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>N2712</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>251</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>N2713</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>252</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>N2714</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>253</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>N2715</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>254</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>N2716</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>255</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>N2668</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>256</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>N2669</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>N2670</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>N2671</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>N2672</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>N2673</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>261</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>N2674</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>N2675</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>N2676</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>264</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>N2677</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>265</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>N2678</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>266</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>N2679</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>267</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>N2630</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>268</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>N2631</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>269</v>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>N2632</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>270</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>N2633</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>271</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>N2634</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>272</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>N2635</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>273</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>N2636</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>274</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>N2637</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>275</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>N2638</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>276</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>N2639</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>277</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>N2640</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>278</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>N2593</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>279</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>N2594</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>N2595</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>N2596</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>282</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>N2597</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>283</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>N2598</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>284</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>N2599</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>285</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>N2600</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>286</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>N2601</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>287</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>N2602</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>288</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>N2603</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
         <is>
           <t>daily</t>
         </is>

--- a/data/Escenarios_Gx/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Escenarios_Gx/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>365</v>
+        <v>1825</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>1825</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47">
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62">
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68">
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84">
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89">
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3351,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3394,12 +3394,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>366</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -3407,12 +3407,12 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>366</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -3420,7 +3420,475 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Solar_PV</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1748</v>
       </c>
     </row>
   </sheetData>
